--- a/server/test-rush-reminders.xlsx
+++ b/server/test-rush-reminders.xlsx
@@ -305,7 +305,7 @@
     <t>Daryl Acera</t>
   </si>
   <si>
-    <t>POLUBI,TRRR</t>
+    <t>Test1, User7</t>
   </si>
   <si>
     <r>

--- a/server/test-rush-reminders.xlsx
+++ b/server/test-rush-reminders.xlsx
@@ -305,7 +305,7 @@
     <t>Daryl Acera</t>
   </si>
   <si>
-    <t>Test1, User7</t>
+    <t>Test1, User8</t>
   </si>
   <si>
     <r>
